--- a/www/download/COUNTRY.GBR.rpA2.xlsx
+++ b/www/download/COUNTRY.GBR.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>Reino Unido</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>0.633524869461459</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>0.640311429707812</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>0.610612454449238</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>0.603715279744235</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>0.617962958901194</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.65958277227438</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>0.694463734373446</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>0.66610712183995</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>0.611856564104196</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>0.545911129989382</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.549329817675818</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.542702541368262</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>0.499580378014237</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.539595512385694</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.639190041391055</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>27.913</t>
+          <t>2.48588980167109</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>28.164</t>
+          <t>2.35386625189373</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>28.63</t>
+          <t>2.58260771160763</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>2.26685930610053</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>29.267</t>
+          <t>2.11590768729931</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29.617</t>
+          <t>1.96774964558204</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>29.925</t>
+          <t>1.85074802159321</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>30.106</t>
+          <t>1.74433814347279</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>30.408</t>
+          <t>1.54300475124499</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30.703</t>
+          <t>1.41189745853257</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>1.43071183506941</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>31.398</t>
+          <t>1.42302745385358</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>31.602</t>
+          <t>1.48938506815238</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>31.674</t>
+          <t>1.73159009016528</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>30.972</t>
+          <t>1.99436974856066</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>23.964</t>
+          <t>1.10908910125164</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>24.245</t>
+          <t>1.1050398778544</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>1.22914716160524</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25.156</t>
+          <t>1.05234079513068</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>25.577</t>
+          <t>0.932450690087375</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>26.013</t>
+          <t>0.862217883751697</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>26.297</t>
+          <t>0.769104700842656</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26.409</t>
+          <t>0.700429055615399</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>26.475</t>
+          <t>0.589673521175199</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>26.731</t>
+          <t>0.503622472258032</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>27.093</t>
+          <t>0.514647286932304</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>27.31</t>
+          <t>0.499554640006631</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>27.438</t>
+          <t>0.524743994256853</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>27.505</t>
+          <t>0.717952953501012</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>26.766</t>
+          <t>0.805219316342827</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>44993.802</t>
+          <t>-0.0131375783806513</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45389.552</t>
+          <t>-0.0259810098948873</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>46176.543</t>
+          <t>0.051704477318784</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>46487.59</t>
+          <t>-0.0152312290883301</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>46808.741</t>
+          <t>-0.0793394659926152</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>47050.896</t>
+          <t>-0.120221125232555</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>47522.65</t>
+          <t>-0.168326650252392</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>47355.712</t>
+          <t>-0.210657138620095</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>47271.276</t>
+          <t>-0.260824648818568</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>47631.936</t>
+          <t>-0.300612622941016</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>48233.604</t>
+          <t>-0.30179436317872</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>48510.801</t>
+          <t>-0.306579087284476</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>48898.444</t>
+          <t>-0.299359668164407</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>48638.184</t>
+          <t>-0.223730561348063</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>47697.788</t>
+          <t>-0.179978437909102</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>38627.754</t>
+          <t>126751777920.97</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>39074.066</t>
+          <t>128929403866.147</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>39982.918</t>
+          <t>128273390657.455</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40493.614</t>
+          <t>130434160564.972</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>40906.739</t>
+          <t>132034772508.381</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>41325.285</t>
+          <t>132942871341.421</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>41761.52</t>
+          <t>131766861986.337</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>41540.623</t>
+          <t>131728566589.835</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>41156.943</t>
+          <t>133452156884.265</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>41469.329</t>
+          <t>138317315579.308</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>42032.235</t>
+          <t>143220699844.943</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>42194.369</t>
+          <t>145657615457.486</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>42455.417</t>
+          <t>146697466362.04</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>42236.584</t>
+          <t>133727290252.894</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>41220.09</t>
+          <t>125086435149.31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>48989347473.4448</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>50566440931.8471</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>49011383364.6447</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>54399366149.1929</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>32.91</t>
+          <t>58710842880.717</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>34.75</t>
+          <t>62467836863.2693</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>66479210058.7923</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>69383974189.3082</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>36.19</t>
+          <t>73894937894.7099</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>35.59</t>
+          <t>78706577380.5966</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>79571927685.8171</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>37.24</t>
+          <t>80831095617.6441</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>80186328260.1844</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>72055265501.6513</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>66099713237.5569</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>41.53</t>
+          <t>2446600.19620342</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>41.62</t>
+          <t>2391296.92082855</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>2217891.41944624</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>43.37</t>
+          <t>2170092.92947845</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>2210800.5949645</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>2279769.61140736</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>2320277.31604314</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>2167574.02817551</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>1953700.57057312</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>1718664.14584193</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>44.49</t>
+          <t>1636139.00225638</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>1554846.84920569</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>1385359.18657786</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>1294329.41877869</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>1479698.64980346</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>267711.810289933</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>268704.9869622</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>275797.851189132</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>279214.749280606</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>292832.108969777</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>298925.440941119</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>290208.67547315</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>298409.927067422</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>319074.443694584</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>346606.788838609</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>373868.005056474</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>393669.47043545</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>445143.636143441</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>483057.709418271</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>447975.637716325</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>42.61</t>
+          <t>552910.182921764</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>42.36</t>
+          <t>560691.825271222</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>548642.820041374</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>45.56</t>
+          <t>551008.4541354</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>47.28</t>
+          <t>575473.555719006</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>49.11</t>
+          <t>582736.65490249</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>50.06</t>
+          <t>557167.772705763</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>564166.528679855</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>611933.411822153</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>687900.840473863</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>757634.255962146</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>801952.324158266</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>54.05</t>
+          <t>905435.795868801</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>54.04</t>
+          <t>901647.535865511</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>779545.01165873</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>1.25519480244501</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>1.23132405757834</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>43.49</t>
+          <t>1.4344117129802</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>42.43</t>
+          <t>1.27629877757849</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>1.18222819609277</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>1.11650695920428</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>1.02888859906627</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>0.968418616858238</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>0.843154497449138</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>41.44</t>
+          <t>0.751834283533135</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>0.772641012898869</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>40.29</t>
+          <t>0.774731922957285</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>0.825982194522748</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>38.04</t>
+          <t>1.03677209029592</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>1.21255854575187</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>212500.162011772</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>224602.795790781</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>237166.043027899</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>253307.032621812</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>252781.185252721</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>239970.98559699</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>221271.799996857</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>228901.138099981</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>249466.205245908</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>297167.948036634</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>300280.684492764</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>303938.098384946</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>358119.468280028</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.633524869461459</t>
+          <t>2044.28924526143</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.640311429707812</t>
+          <t>2085.64408875426</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.610612454449238</t>
+          <t>1977.06266093766</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.603715279744235</t>
+          <t>2162.48076598795</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.617962958901194</t>
+          <t>2295.45462254045</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.65958277227438</t>
+          <t>2401.40840592278</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.694463734373446</t>
+          <t>2528.01498493335</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.66610712183995</t>
+          <t>2627.2851751035</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.611856564104196</t>
+          <t>2791.12135579641</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.545911129989382</t>
+          <t>2944.39330292906</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.549329817675818</t>
+          <t>2936.99212659422</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.542702541368262</t>
+          <t>2959.76183147726</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.499580378014237</t>
+          <t>2922.45529047979</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.539595512385694</t>
+          <t>2619.71516093987</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.639190041391055</t>
+          <t>2469.54020912938</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>47005847178.8675</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>51912469630.4493</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>49855711263.9276</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>53620822891.1956</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>58077166031.6264</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>60791327378.2451</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>63840354798.619</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>66295883421.9525</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.008</t>
+          <t>74089183969.2497</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.188</t>
+          <t>81465054740.1562</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.246</t>
+          <t>79208458826.4117</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.327</t>
+          <t>82454572186.8104</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>82385555287.3826</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>78715805525.2852</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.223</t>
+          <t>66913133111.4637</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>43700680815.1357</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>47653452588.135</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>43917924442.5929</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>46612156272.0939</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>48980222720.0954</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.914</t>
+          <t>51011278310.7306</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.921</t>
+          <t>52961664602.7783</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.003</t>
+          <t>53297640935.5347</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.156</t>
+          <t>59192379227.9464</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>64883504690.1984</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.426</t>
+          <t>64693160033.5296</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>65489214219.9286</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>61868435396.4102</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.658</t>
+          <t>58926752636.5411</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.416</t>
+          <t>49550674409.9666</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.764</t>
+          <t>3305166363.73186</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.874</t>
+          <t>4259017042.31436</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3.104</t>
+          <t>5937786821.33465</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3.286</t>
+          <t>7008666619.10174</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3.374</t>
+          <t>9096943311.531</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.316</t>
+          <t>9780049067.51444</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>10878690195.8407</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.579</t>
+          <t>12998242486.4178</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4.115</t>
+          <t>14896804741.3032</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>4.905</t>
+          <t>16581550049.9578</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>5.125</t>
+          <t>14515298792.8821</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>5.395</t>
+          <t>16965357966.8817</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>6.298</t>
+          <t>20517119890.9725</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19789052888.744</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17362458701.497</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2.101</t>
+          <t>4610.27048060779</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.221</t>
+          <t>4653.74783078345</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>4812.98449908246</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.637</t>
+          <t>4922.45232415537</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.712</t>
+          <t>5009.20580015925</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.688</t>
+          <t>5082.59760302721</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.669</t>
+          <t>5129.06078119997</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.909</t>
+          <t>5171.59705046938</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.332</t>
+          <t>5144.46787986249</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3.942</t>
+          <t>5158.08913227648</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>4.192</t>
+          <t>5206.23269816198</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4.487</t>
+          <t>5252.78380667322</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5336.3513247049</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>4.909</t>
+          <t>5335.76272432741</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4.002</t>
+          <t>5464.00229378706</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.048</t>
+          <t>4578.45882748932</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>4622.62345353814</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.217</t>
+          <t>4781.99871132001</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>4897.32813731538</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.343</t>
+          <t>4984.7638759838</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>5060.8811789395</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>5103.75789190971</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>5145.62968399177</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>5117.67180929911</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2.005</t>
+          <t>5128.95775069399</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2.073</t>
+          <t>5176.83461595991</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2.225</t>
+          <t>5226.17820080272</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2.557</t>
+          <t>5306.52220619039</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.452</t>
+          <t>5304.41586511968</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2.008</t>
+          <t>5434.21414029163</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>248.59</t>
+          <t>302968.846362564</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>235.39</t>
+          <t>334168.171598558</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>258.26</t>
+          <t>362418.111046132</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>226.69</t>
+          <t>360604.193608908</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>211.59</t>
+          <t>365500.987238348</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>196.77</t>
+          <t>378672.434444504</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>185.07</t>
+          <t>368615.603568295</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>174.43</t>
+          <t>386747.802219923</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>154.3</t>
+          <t>443194.281960158</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>141.19</t>
+          <t>523620.734790844</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>143.07</t>
+          <t>547244.802844159</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>607572.724619445</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>148.94</t>
+          <t>703544.645994065</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>173.16</t>
+          <t>737461.648794785</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>199.44</t>
+          <t>572279.820996099</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>110.91</t>
+          <t>22722159703.8545</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>24461232231.3135</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>122.91</t>
+          <t>24009169587.2732</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>105.23</t>
+          <t>22918963406.4885</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>93.25</t>
+          <t>22885910700.1752</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>86.22</t>
+          <t>24358831103.2987</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>76.91</t>
+          <t>23603386788.201</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>70.04</t>
+          <t>22913623060.1928</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>23877355126.1664</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>50.36</t>
+          <t>23633065675.8021</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>51.46</t>
+          <t>23350819293.782</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>24263048825.9899</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>24554974491.8077</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>24301804432.9614</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>80.52</t>
+          <t>20755673060.0193</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>286045.401442143</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>313056.00743486</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>330836.790070265</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>345103.027382917</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-7.93</t>
+          <t>356517.811334066</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-12.02</t>
+          <t>372960.94236261</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-16.83</t>
+          <t>369101.953496387</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-21.07</t>
+          <t>391838.926787815</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-26.08</t>
+          <t>441883.051931132</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-30.06</t>
+          <t>534548.962064389</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-30.18</t>
+          <t>574998.747413278</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-30.66</t>
+          <t>632001.053436416</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-29.94</t>
+          <t>729681.255202372</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-22.37</t>
+          <t>748582.506174736</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>577281.317174778</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>127800.297</t>
+          <t>64861205935.7093</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>130190.111</t>
+          <t>70431485648.0935</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>136909.287</t>
+          <t>65597348945.4751</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>141433.172</t>
+          <t>72221100132.3953</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>145890.258</t>
+          <t>78363973618.086</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>149888.606</t>
+          <t>83461697871.688</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>152728.69</t>
+          <t>87596062108.5198</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>154913.707</t>
+          <t>90801201431.4672</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>155619.001</t>
+          <t>97578293670.6595</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>157476.428</t>
+          <t>108098212580.061</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>160949.123</t>
+          <t>109655464056.419</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>164092.928</t>
+          <t>112457827816.535</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>167696.641</t>
+          <t>112393068571.105</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>168011.023</t>
+          <t>105115931467.934</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>168309.847</t>
+          <t>88721179979.7192</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>110480.522</t>
+          <t>16923.4449204217</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>112830.116</t>
+          <t>21112.1641636981</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>119313.886</t>
+          <t>31581.3209758671</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>123829.211</t>
+          <t>15501.166225991</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>128120.457</t>
+          <t>8983.17590428165</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>132213.611</t>
+          <t>5711.49208189395</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>134878.911</t>
+          <t>-486.349928091777</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>136576.707</t>
+          <t>-5091.12456789178</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>136199.787</t>
+          <t>1311.23002902552</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>137880.881</t>
+          <t>-10928.2272735449</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>141052.462</t>
+          <t>-27753.9445691197</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>143453.526</t>
+          <t>-24428.3288169715</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>146418.808</t>
+          <t>-26136.6092083064</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>146760.154</t>
+          <t>-11120.8573799519</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>146249.485</t>
+          <t>-5001.49617867885</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>126751.778</t>
+          <t>-42139046231.8549</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>128929.404</t>
+          <t>-45970253416.78</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>128273.391</t>
+          <t>-41588179358.2019</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>130434.161</t>
+          <t>-49302136725.9068</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>132034.773</t>
+          <t>-55478062917.9108</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>132942.871</t>
+          <t>-59102866768.3893</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>131766.862</t>
+          <t>-63992675320.3188</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>131728.567</t>
+          <t>-67887578371.2743</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>133452.157</t>
+          <t>-73700938544.4931</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>138317.316</t>
+          <t>-84465146904.2591</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>143220.7</t>
+          <t>-86304644762.6367</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>145657.615</t>
+          <t>-88194778990.5453</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>146697.466</t>
+          <t>-87838094079.2972</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>133727.29</t>
+          <t>-80814127034.9728</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>125086.435</t>
+          <t>-67965506919.6999</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>497131.41044</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>516670.71791</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.549</t>
+          <t>559244.04591</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>578765.90324</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>580780.17479</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>570505.03286</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>556625.6481</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>594832.15011</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.612</t>
+          <t>671468.75727</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>786803.00218</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.758</t>
+          <t>820056.55398</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>876941.47773</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.905</t>
+          <t>989863.96314</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>939376.0817</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>748813.66309</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>61371.537</t>
+          <t>0.0470951134000004</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>61787.906</t>
+          <t>0.0509666180847551</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>64481.889</t>
+          <t>0.0554210457307447</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>66095.431</t>
+          <t>0.0539449418750565</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>67186.442</t>
+          <t>0.0526766993459328</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>68195.481</t>
+          <t>0.0516571223830756</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>68632.624</t>
+          <t>0.0545793368206159</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>69676.434</t>
+          <t>0.0633824406813315</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>69584.651</t>
+          <t>0.0679132053844368</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>69692.778</t>
+          <t>0.070261039215943</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>70674.784</t>
+          <t>0.0675504766851976</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>71501.702</t>
+          <t>0.0737477222730851</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>72121.562</t>
+          <t>0.0710262202283211</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>71644.402</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>71882.54</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>609344.664262209</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>630766.500194064</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>704156.9451464</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>772019.549801978</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>802302.130258525</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>806841.874751881</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>812416.796848852</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>881834.139782243</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>1008231.40487965</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>1188319.79474407</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>1246278.60661961</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>1327141.80120477</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>1520317.19677425</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>1439534.76037267</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>1222888.6709742</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>48989.347</t>
+          <t>704861.697415182</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>50566.441</t>
+          <t>729241.42651865</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>49011.383</t>
+          <t>808232.241464891</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>54399.366</t>
+          <t>880232.972086167</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>58710.843</t>
+          <t>912758.829648804</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>62467.837</t>
+          <t>914475.288209213</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>66479.21</t>
+          <t>920938.425083602</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>69383.974</t>
+          <t>1002647.46318871</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>73894.938</t>
+          <t>1155969.91713234</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>78706.577</t>
+          <t>1362823.71365045</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>79571.928</t>
+          <t>1426225.38972571</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>80831.096</t>
+          <t>1522740.61097274</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>80186.328</t>
+          <t>1751292.93512564</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>72055.266</t>
+          <t>1657762.14653244</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>66099.713</t>
+          <t>1415851.85917085</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>125.52</t>
+          <t>2763663.07938533</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>123.13</t>
+          <t>2874492.27388289</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>143.44</t>
+          <t>3103675.08207785</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>127.63</t>
+          <t>3285574.5211948</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>118.22</t>
+          <t>3373543.96830096</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>111.65</t>
+          <t>3316084.58972</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>102.89</t>
+          <t>3249801.39741351</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.84</t>
+          <t>3578671.50054565</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>4115301.26386587</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>75.18</t>
+          <t>4904674.42694353</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>77.26</t>
+          <t>5124591.48593073</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>77.47</t>
+          <t>5394953.78242375</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>6297565.08436557</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>103.68</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>121.26</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2.447</t>
+          <t>704861.697415182</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.391</t>
+          <t>717204.956011211</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.218</t>
+          <t>739668.828371792</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>774560.756860511</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.211</t>
+          <t>809994.425963053</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>863088.268945091</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>893154.834139379</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.168</t>
+          <t>890083.004289131</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.954</t>
+          <t>912867.143363989</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.719</t>
+          <t>938179.502041366</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>978614.593700576</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1009930.5478757</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1041060.7112423</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.294</t>
+          <t>1032442.29769058</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1023323.8990226</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>609344.664262209</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>620383.656677345</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>643756.219903232</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>678743.230153769</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>711910.160967824</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>762181.992895343</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>789673.831616382</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>785132.006246717</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>799473.780840878</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>822591.64493767</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>858082.963645492</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>883884.88869262</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>909819.950108982</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>903492.72797568</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>889808.724787288</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>342655.188134818</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>371105.94570135</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>409174.961685109</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>430547.159193833</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>430488.346601196</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>411270.373080787</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>398643.805066398</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>455726.072201287</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>528949.505197663</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>641775.470289546</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>646449.28218429</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>701803.651607263</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>805411.712864362</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>793923.820217562</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>592527.649649153</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>110480521797.285</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>112830116157.345</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>119313885732.254</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>123829210666.453</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>128120456750.673</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>132213611447.547</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>134878911363.216</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>136576706505.846</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>136199787119.359</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>137880880594.883</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>141052462491.302</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>143453525760.246</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>146418807647.253</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>146760153732.626</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>146249485395.504</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>127800296534.874</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>130190110772.353</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>136909286977.464</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>141433172204.86</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>145890258014.851</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>149888606436.505</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>152728690163.227</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>154913707423.787</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>155619000538.951</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>157476427614.686</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>160949123291.917</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>164092927522.042</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>167696640778.55</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>168011022791.349</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>168309847487.683</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>61371537318.0095</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>61787905982.2907</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>64481889155.867</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>66095431324.9535</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>67186442377.2982</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>68195480928.4519</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>68632624429.4507</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>69676434085.4315</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>69584650707.1666</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>69692778047.3355</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>70674783924.364</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>71501702301.598</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>72121561669.3942</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>71644401993.8083</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>71882540094.0482</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>27913387.7468886</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>28163684.9898958</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>28630138.8273842</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>28879660.1410479</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>29267235.4487518</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>29617096.5365194</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>29924752.1919734</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>30105879.5400161</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>30408163.3871446</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>30703397.31174</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>31090257.8953786</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>31398264.8920847</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>31601986.058387</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>31673802.9339179</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>30972251.5790757</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>23964000</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>24245000</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>24790000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>25156000</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>25577000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>26013000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>26297000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>26409000</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>26475000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>26731000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>27093000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>27310000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>27438000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>27505000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>26766000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>44993802000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>45389552000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>46176543000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>46487590000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>46808741000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>47050896000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>47522650000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>47355712000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>47271276000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>47631936000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>48233604000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>48510801000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>48898444000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>48638184000</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>47697788000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>38627753854.3556</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>39074066076.0412</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>39982918276.1454</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>40493614132.8693</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>40906739232.4566</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>41325285081.1633</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>41761519662.1478</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>41540623204.3714</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>41156942501.4695</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>41469328891.795</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>42032235228.4587</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>42194369015.7217</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>42455417327.0363</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>42236584401.0295</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>41220089871.3641</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.277767528904053</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.28488409319564</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.299234247700508</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.316493571632793</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.329116537176529</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.347523843868929</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.350137638080635</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.360656736409175</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.361891037278401</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.355932378530736</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.361792155573614</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.372400404706165</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.389528465053993</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.399501116619149</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.398407637829891</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.415303017138807</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.416234283839518</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.435409014035973</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.433675026228324</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.432040079440748</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.420134869664512</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.412186031559375</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.413691429736799</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.431608389644541</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.446891177916702</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.444916896543453</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.442551596604485</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.422380180206385</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.417104646342857</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.427590105531019</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.30692945395714</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.298881622964842</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.265356738263519</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.249831402138882</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.238843383382723</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.232341286466559</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.23767633035999</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.225651833854026</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.206500573077058</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.197176443552562</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.193290947882933</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.185047998689349</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.188091354739622</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.183394237037994</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.17400225663909</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.426055835058621</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.42355353090756</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.437324958328552</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.455572437960996</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.472839803087316</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.491061196832171</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.500607267965176</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.51095058544482</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.50726261102816</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.498522322896714</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.50434538558141</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.51603369333474</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.54048769495447</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.540414298050232</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.543479078583824</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.423198456607996</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.429484250721709</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.434865854864508</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.424302374678086</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.414960978830764</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.401713787845467</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.391698076797508</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.389023972510903</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.402012900664355</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.414364820017456</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.41098262601955</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.402893210446118</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.378642327524046</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.380355654501915</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.381639115268523</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.150745708333383</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.146962218370731</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.12780918680694</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.120125187360918</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.11219921808192</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.107225015322362</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.107694655237316</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.100025442044277</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0907244883074844</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0871128570858303</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0846719883990402</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0810730962191419</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0808699775214841</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0792300474478532</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0748818061476529</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2101260.81717</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2220947.3865</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2459925.23759</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2637347.57813</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2712196.54421</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2687524.70806</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2668744.08914</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2908661.31497</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>3332392.14615</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>3941733.15299</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>4191589.31804</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>4487219.69286</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>5139696.58206</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>4908990.5134</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>4002420.38558</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1047516.88555</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1100347.37222</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1217407.20315</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1310780.13128</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1343247.17625</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1325745.66129</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1319582.23015</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1458373.53539</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1684919.42233</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2004599.18394</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2072674.67191</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2224544.26258</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2556704.64799</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2451685.96675</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2008379.50882</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1750849.27053902</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1797714.07422874</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1850266.51528009</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1921140.27809232</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1991368.44787993</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2066078.15091517</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2140835.62887224</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2215228.67333853</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2284620.07971019</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2361715.48426028</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2443562.40256436</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2531603.63459202</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2632783.32126529</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
